--- a/records/pop_talks.xlsx
+++ b/records/pop_talks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juliu\Github\YHLin-Altair1999.github.io\records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02378C0E-6821-4207-80A2-5E3D55E37383}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAE1A10-E99A-4E7E-97A0-83DEB02851E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,6 +107,66 @@
   </si>
   <si>
     <t>Astrophysical Black Holes</t>
+  </si>
+  <si>
+    <t>Galaxies and where to find them</t>
+  </si>
+  <si>
+    <t>Taipei Astronomy Museum</t>
+  </si>
+  <si>
+    <t>3-hour lecture in English for high school students</t>
+  </si>
+  <si>
+    <t>Popular Science Writing</t>
+  </si>
+  <si>
+    <t>HCHS Astronomy Club</t>
+  </si>
+  <si>
+    <t>Malaysia Olympiad on Astronomy and Astrophysics 2026 guest lecture</t>
+  </si>
+  <si>
+    <t>Radiative Processes</t>
+  </si>
+  <si>
+    <t>Galaxy formation and evolution</t>
+  </si>
+  <si>
+    <t>NTHU AstroRead</t>
+  </si>
+  <si>
+    <t>ExoClock</t>
+  </si>
+  <si>
+    <t>Taiwan astronomical Observation collaboration Platform (TOP)</t>
+  </si>
+  <si>
+    <t>Crash Course of Cosmology</t>
+  </si>
+  <si>
+    <t>HCHS Earth Science Competition team</t>
+  </si>
+  <si>
+    <t>How I became an Amateur Planet Hunter</t>
+  </si>
+  <si>
+    <t>Astronomy On Tap San Diego</t>
+  </si>
+  <si>
+    <t>NTU Astronomy Club</t>
+  </si>
+  <si>
+    <t>Malaysia Olympiad on Astronomy and Astrophysics 2025 guest lecture</t>
+  </si>
+  <si>
+    <t>Observation of Cosmology</t>
+  </si>
+  <si>
+    <t>A Physicist's view to Space Technologies</t>
+  </si>
+  <si>
+    <t>NTHU Astronomy Camp</t>
   </si>
 </sst>
 </file>
@@ -114,19 +174,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -152,12 +212,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -435,15 +496,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,141 +518,265 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
+        <v>46061</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1">
+        <v>45811</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
+        <v>45783</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>45710</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>45506</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
         <v>45223</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C13" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
         <v>45202</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="15" spans="1:4">
+      <c r="A15" s="1">
         <v>44971</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="16" spans="1:4">
+      <c r="A16" s="1">
         <v>44969</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B16" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
         <v>44969</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="18" spans="1:3">
+      <c r="A18" s="1">
         <v>44965</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="19" spans="1:3">
+      <c r="A19" s="1">
         <v>44838</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B19" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="20" spans="1:3">
+      <c r="A20" s="1">
         <v>44752</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="21" spans="1:3">
+      <c r="A21" s="1">
         <v>44614</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+    <row r="22" spans="1:3">
+      <c r="A22" s="1">
         <v>44599</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="23" spans="1:3">
+      <c r="A23" s="1">
         <v>44576</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B23" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
         <v>44558</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C24" t="s">
         <v>5</v>
       </c>
     </row>
